--- a/output_plant/stomata_Intermediate_kuerschner_1996.xlsx
+++ b/output_plant/stomata_Intermediate_kuerschner_1996.xlsx
@@ -606,7 +606,7 @@
     <t xml:space="preserve">10.1016/0377-8398(95)00067-4</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-si_kuerschner_1996.xlsx</t>
+    <t xml:space="preserve">stomata-si_kuerschner_1996_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>

--- a/output_plant/stomata_Intermediate_kuerschner_1996.xlsx
+++ b/output_plant/stomata_Intermediate_kuerschner_1996.xlsx
@@ -615,7 +615,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ages only shown graphically; they are updated here based on the biostratigraphy using GTS2020</t>
+    <t xml:space="preserve">Ages only shown graphically; they are updated here based on the biostratigraphy using GTS2020; Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Fagaceae / Quercus</t>
